--- a/samurai_blue_2026_members.xlsx
+++ b/samurai_blue_2026_members.xlsx
@@ -2,9 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" tabRatio="600" firstSheet="0" activeTab="4" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Members" sheetId="1" state="visible" r:id="rId1"/>
@@ -22,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -33,18 +32,18 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="000B1F3A"/>
+      <color rgb="FF0B1F3A"/>
       <sz val="12"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -53,11 +52,17 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="000B1F3A"/>
+      <color rgb="FF0B1F3A"/>
       <sz val="14"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -66,32 +71,45 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="000B1F3A"/>
+        <fgColor rgb="FF0B1F3A"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FDF3D0"/>
+        <fgColor rgb="FFFDF3D0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E3EFFB"/>
+        <fgColor rgb="FFE3EFFB"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E8F5E9"/>
+        <fgColor rgb="FFE8F5E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000B1F3A"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
+    <border/>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
+      <left style="thin">
+        <color rgb="FFD9CBA3"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD9CBA3"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD9CBA3"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD9CBA3"/>
+      </bottom>
     </border>
     <border>
       <left style="thin">
@@ -111,30 +129,30 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -144,9 +162,21 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -225,10 +255,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:sysClr val="windowText"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr val="window"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -358,6 +388,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -381,10 +412,11 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="95000"/>
@@ -393,13 +425,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="25400" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -475,6 +507,7 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -494,12 +527,11 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
@@ -509,8 +541,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R27"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:T27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
@@ -530,6 +562,8 @@
     <col width="60" customWidth="1" min="16" max="16"/>
     <col width="50" customWidth="1" min="17" max="17"/>
     <col width="13" customWidth="1" min="18" max="18"/>
+    <col width="34" customWidth="1" min="19" max="19"/>
+    <col width="42" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -623,8 +657,18 @@
           <t>備考</t>
         </is>
       </c>
-    </row>
-    <row r="2">
+      <c r="S1" s="13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T1" s="13" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="89.25" customHeight="1">
       <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
@@ -701,8 +745,18 @@
         </is>
       </c>
       <c r="R2" s="4" t="inlineStr"/>
-    </row>
-    <row r="3">
+      <c r="S2" s="15" t="inlineStr">
+        <is>
+          <t>https://x.com/SuzukiZion</t>
+        </is>
+      </c>
+      <c r="T2" s="15" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/zionsuzuki/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="89.25" customHeight="1">
       <c r="A3" s="2" t="n">
         <v>12</v>
       </c>
@@ -779,8 +833,18 @@
         </is>
       </c>
       <c r="R3" s="4" t="inlineStr"/>
-    </row>
-    <row r="4">
+      <c r="S3" s="15" t="inlineStr">
+        <is>
+          <t>https://x.com/keisuke_0728</t>
+        </is>
+      </c>
+      <c r="T3" s="15" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/keisuke.osako/</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="89.25" customHeight="1">
       <c r="A4" s="2" t="n">
         <v>23</v>
       </c>
@@ -857,8 +921,18 @@
         </is>
       </c>
       <c r="R4" s="4" t="inlineStr"/>
-    </row>
-    <row r="5">
+      <c r="S4" s="15" t="inlineStr">
+        <is>
+          <t>https://x.com/TH1_official</t>
+        </is>
+      </c>
+      <c r="T4" s="15" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/tomoki.hayakawa_official/</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="89.25" customHeight="1">
       <c r="A5" s="2" t="n">
         <v>2</v>
       </c>
@@ -935,8 +1009,18 @@
         </is>
       </c>
       <c r="R5" s="4" t="inlineStr"/>
-    </row>
-    <row r="6">
+      <c r="S5" s="15" t="inlineStr">
+        <is>
+          <t>https://x.com/ssggwwrrr</t>
+        </is>
+      </c>
+      <c r="T5" s="15" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/yukinarisugawara/</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="89.25" customHeight="1">
       <c r="A6" s="2" t="n">
         <v>3</v>
       </c>
@@ -1013,8 +1097,14 @@
         </is>
       </c>
       <c r="R6" s="4" t="inlineStr"/>
-    </row>
-    <row r="7">
+      <c r="S6" s="15" t="inlineStr"/>
+      <c r="T6" s="15" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/shogo_taniguchi_5/</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="89.25" customHeight="1">
       <c r="A7" s="2" t="n">
         <v>4</v>
       </c>
@@ -1091,8 +1181,14 @@
         </is>
       </c>
       <c r="R7" s="4" t="inlineStr"/>
-    </row>
-    <row r="8">
+      <c r="S7" s="15" t="inlineStr"/>
+      <c r="T7" s="15" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/kouitakura/</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="89.25" customHeight="1">
       <c r="A8" s="2" t="n">
         <v>16</v>
       </c>
@@ -1169,8 +1265,18 @@
         </is>
       </c>
       <c r="R8" s="4" t="inlineStr"/>
-    </row>
-    <row r="9">
+      <c r="S8" s="15" t="inlineStr">
+        <is>
+          <t>https://x.com/tsuyoshi4w</t>
+        </is>
+      </c>
+      <c r="T8" s="15" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/tys_w0205/</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="89.25" customHeight="1">
       <c r="A9" s="2" t="n">
         <v>22</v>
       </c>
@@ -1247,8 +1353,14 @@
         </is>
       </c>
       <c r="R9" s="4" t="inlineStr"/>
-    </row>
-    <row r="10">
+      <c r="S9" s="15" t="inlineStr"/>
+      <c r="T9" s="15" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/tomiyasu.t/</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="89.25" customHeight="1">
       <c r="A10" s="2" t="n">
         <v>21</v>
       </c>
@@ -1325,8 +1437,14 @@
         </is>
       </c>
       <c r="R10" s="4" t="inlineStr"/>
-    </row>
-    <row r="11">
+      <c r="S10" s="15" t="inlineStr"/>
+      <c r="T10" s="15" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/hiroki_ito38/</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="89.25" customHeight="1">
       <c r="A11" s="2" t="n">
         <v>20</v>
       </c>
@@ -1403,8 +1521,18 @@
         </is>
       </c>
       <c r="R11" s="4" t="inlineStr"/>
-    </row>
-    <row r="12">
+      <c r="S11" s="15" t="inlineStr">
+        <is>
+          <t>https://x.com/ayumucrz</t>
+        </is>
+      </c>
+      <c r="T11" s="15" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ayumuseko_00/</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="89.25" customHeight="1">
       <c r="A12" s="2" t="n">
         <v>5</v>
       </c>
@@ -1481,8 +1609,18 @@
         </is>
       </c>
       <c r="R12" s="4" t="inlineStr"/>
-    </row>
-    <row r="13">
+      <c r="S12" s="15" t="inlineStr">
+        <is>
+          <t>https://x.com/YutoNagatomo5</t>
+        </is>
+      </c>
+      <c r="T12" s="15" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/yutonagatomo55/</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="102" customHeight="1">
       <c r="A13" s="2" t="n">
         <v>25</v>
       </c>
@@ -1559,8 +1697,14 @@
         </is>
       </c>
       <c r="R13" s="4" t="inlineStr"/>
-    </row>
-    <row r="14">
+      <c r="S13" s="15" t="inlineStr"/>
+      <c r="T13" s="15" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/junnosuke0712/</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="89.25" customHeight="1">
       <c r="A14" s="2" t="n">
         <v>14</v>
       </c>
@@ -1637,8 +1781,18 @@
         </is>
       </c>
       <c r="R14" s="4" t="inlineStr"/>
-    </row>
-    <row r="15">
+      <c r="S14" s="15" t="inlineStr">
+        <is>
+          <t>https://x.com/ItouJky</t>
+        </is>
+      </c>
+      <c r="T14" s="15" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/1409junya/</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="89.25" customHeight="1">
       <c r="A15" s="2" t="n">
         <v>15</v>
       </c>
@@ -1715,8 +1869,14 @@
         </is>
       </c>
       <c r="R15" s="4" t="inlineStr"/>
-    </row>
-    <row r="16">
+      <c r="S15" s="15" t="inlineStr"/>
+      <c r="T15" s="15" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/kamadadaichi/</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="89.25" customHeight="1">
       <c r="A16" s="2" t="n">
         <v>19</v>
       </c>
@@ -1793,8 +1953,14 @@
         </is>
       </c>
       <c r="R16" s="4" t="inlineStr"/>
-    </row>
-    <row r="17">
+      <c r="S16" s="15" t="inlineStr"/>
+      <c r="T16" s="15" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/koki4629/</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="89.25" customHeight="1">
       <c r="A17" s="2" t="n">
         <v>11</v>
       </c>
@@ -1871,8 +2037,18 @@
         </is>
       </c>
       <c r="R17" s="4" t="inlineStr"/>
-    </row>
-    <row r="18">
+      <c r="S17" s="15" t="inlineStr">
+        <is>
+          <t>https://x.com/M_daizen_1020</t>
+        </is>
+      </c>
+      <c r="T17" s="15" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/m_daizen0827/</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="89.25" customHeight="1">
       <c r="A18" s="2" t="n">
         <v>10</v>
       </c>
@@ -1949,8 +2125,18 @@
         </is>
       </c>
       <c r="R18" s="4" t="inlineStr"/>
-    </row>
-    <row r="19">
+      <c r="S18" s="15" t="inlineStr">
+        <is>
+          <t>https://x.com/doan_ritsu</t>
+        </is>
+      </c>
+      <c r="T18" s="15" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/doanritsu/</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="89.25" customHeight="1">
       <c r="A19" s="2" t="n">
         <v>18</v>
       </c>
@@ -2027,8 +2213,14 @@
         </is>
       </c>
       <c r="R19" s="4" t="inlineStr"/>
-    </row>
-    <row r="20">
+      <c r="S19" s="15" t="inlineStr"/>
+      <c r="T19" s="15" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/bee18_official/</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="89.25" customHeight="1">
       <c r="A20" s="2" t="n">
         <v>7</v>
       </c>
@@ -2105,8 +2297,14 @@
         </is>
       </c>
       <c r="R20" s="4" t="inlineStr"/>
-    </row>
-    <row r="21">
+      <c r="S20" s="15" t="inlineStr"/>
+      <c r="T20" s="15" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/tnk_0910/</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="89.25" customHeight="1">
       <c r="A21" s="2" t="n">
         <v>6</v>
       </c>
@@ -2187,8 +2385,18 @@
           <t>6/12追加招集</t>
         </is>
       </c>
-    </row>
-    <row r="22">
+      <c r="S21" s="15" t="inlineStr">
+        <is>
+          <t>https://x.com/shuto_machino</t>
+        </is>
+      </c>
+      <c r="T21" s="15" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/machino9.30/</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="89.25" customHeight="1">
       <c r="A22" s="2" t="n">
         <v>13</v>
       </c>
@@ -2265,8 +2473,14 @@
         </is>
       </c>
       <c r="R22" s="4" t="inlineStr"/>
-    </row>
-    <row r="23">
+      <c r="S22" s="15" t="inlineStr"/>
+      <c r="T22" s="15" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nakamura.keito/</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="89.25" customHeight="1">
       <c r="A23" s="2" t="n">
         <v>24</v>
       </c>
@@ -2343,8 +2557,14 @@
         </is>
       </c>
       <c r="R23" s="4" t="inlineStr"/>
-    </row>
-    <row r="24">
+      <c r="S23" s="15" t="inlineStr"/>
+      <c r="T23" s="15" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/kaishusano_1230/</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="89.25" customHeight="1">
       <c r="A24" s="2" t="n">
         <v>8</v>
       </c>
@@ -2421,8 +2641,14 @@
         </is>
       </c>
       <c r="R24" s="4" t="inlineStr"/>
-    </row>
-    <row r="25">
+      <c r="S24" s="15" t="inlineStr"/>
+      <c r="T24" s="15" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/takefusa.kubo/</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="89.25" customHeight="1">
       <c r="A25" s="2" t="n">
         <v>17</v>
       </c>
@@ -2499,8 +2725,14 @@
         </is>
       </c>
       <c r="R25" s="4" t="inlineStr"/>
-    </row>
-    <row r="26">
+      <c r="S25" s="15" t="inlineStr"/>
+      <c r="T25" s="15" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/yuiton.s/</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="89.25" customHeight="1">
       <c r="A26" s="2" t="n">
         <v>26</v>
       </c>
@@ -2577,8 +2809,14 @@
         </is>
       </c>
       <c r="R26" s="4" t="inlineStr"/>
-    </row>
-    <row r="27">
+      <c r="S26" s="15" t="inlineStr"/>
+      <c r="T26" s="15" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/shio_kenken/</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="89.25" customHeight="1">
       <c r="A27" s="2" t="n">
         <v>9</v>
       </c>
@@ -2655,6 +2893,12 @@
         </is>
       </c>
       <c r="R27" s="4" t="inlineStr"/>
+      <c r="S27" s="15" t="inlineStr"/>
+      <c r="T27" s="15" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/keisuke.0603_42/</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2667,15 +2911,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:D9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="56" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="15" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>役職</t>
@@ -2691,140 +2936,185 @@
           <t>Name</t>
         </is>
       </c>
-    </row>
-    <row r="2">
+      <c r="D1" s="13" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="15" customHeight="1">
       <c r="A2" s="9" t="inlineStr">
         <is>
           <t>監督</t>
         </is>
       </c>
-      <c r="B2" s="10" t="inlineStr">
+      <c r="B2" s="12" t="inlineStr">
         <is>
           <t>森保 一</t>
         </is>
       </c>
-      <c r="C2" s="10" t="inlineStr">
+      <c r="C2" s="12" t="inlineStr">
         <is>
           <t>MORIYASU Hajime</t>
         </is>
       </c>
-    </row>
-    <row r="3">
+      <c r="D2" s="14" t="inlineStr">
+        <is>
+          <t>https://www.jfa.jp/national_team/staff/MORIYASU_Hajime.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
         <is>
           <t>コーチ</t>
         </is>
       </c>
-      <c r="B3" s="10" t="inlineStr">
+      <c r="B3" s="12" t="inlineStr">
         <is>
           <t>名波 浩</t>
         </is>
       </c>
-      <c r="C3" s="10" t="inlineStr">
+      <c r="C3" s="12" t="inlineStr">
         <is>
           <t>NANAMI Hiroshi</t>
         </is>
       </c>
-    </row>
-    <row r="4">
+      <c r="D3" s="14" t="inlineStr">
+        <is>
+          <t>https://www.jfa.jp/national_team/staff/NANAMI_Hiroshi.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
         <is>
           <t>コーチ</t>
         </is>
       </c>
-      <c r="B4" s="10" t="inlineStr">
+      <c r="B4" s="12" t="inlineStr">
         <is>
           <t>齊藤 俊秀</t>
         </is>
       </c>
-      <c r="C4" s="10" t="inlineStr">
+      <c r="C4" s="12" t="inlineStr">
         <is>
           <t>SAITO Toshihide</t>
         </is>
       </c>
-    </row>
-    <row r="5">
+      <c r="D4" s="14" t="inlineStr">
+        <is>
+          <t>https://www.jfa.jp/national_team/staff/SAITO_Toshihide.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
       <c r="A5" s="9" t="inlineStr">
         <is>
           <t>コーチ</t>
         </is>
       </c>
-      <c r="B5" s="10" t="inlineStr">
+      <c r="B5" s="12" t="inlineStr">
         <is>
           <t>中村 俊輔</t>
         </is>
       </c>
-      <c r="C5" s="10" t="inlineStr">
+      <c r="C5" s="12" t="inlineStr">
         <is>
           <t>NAKAMURA Shunsuke</t>
         </is>
       </c>
-    </row>
-    <row r="6">
+      <c r="D5" s="14" t="inlineStr">
+        <is>
+          <t>https://ja.wikipedia.org/wiki/%E4%B8%AD%E6%9D%91%E4%BF%8A%E8%BC%94</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
       <c r="A6" s="9" t="inlineStr">
         <is>
           <t>コーチ</t>
         </is>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>前田 遼一</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C6" s="12" t="inlineStr">
         <is>
           <t>MAEDA Ryoichi</t>
         </is>
       </c>
-    </row>
-    <row r="7">
+      <c r="D6" s="14" t="inlineStr">
+        <is>
+          <t>https://www.jfa.jp/national_team/staff/MAEDA_Ryoichi.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
       <c r="A7" s="9" t="inlineStr">
         <is>
           <t>コーチ</t>
         </is>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="12" t="inlineStr">
         <is>
           <t>長谷部 誠</t>
         </is>
       </c>
-      <c r="C7" s="10" t="inlineStr">
+      <c r="C7" s="12" t="inlineStr">
         <is>
           <t>HASEBE Makoto</t>
         </is>
       </c>
-    </row>
-    <row r="8">
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t>https://ja.wikipedia.org/wiki/%E9%95%B7%E8%B0%B7%E9%83%A8%E8%AA%A0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
       <c r="A8" s="9" t="inlineStr">
         <is>
           <t>フィジカルコーチ</t>
         </is>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="12" t="inlineStr">
         <is>
           <t>松本 良一</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C8" s="12" t="inlineStr">
         <is>
           <t>MATSUMOTO Ryoichi</t>
         </is>
       </c>
-    </row>
-    <row r="9">
+      <c r="D8" s="14" t="inlineStr">
+        <is>
+          <t>https://www.jfa.jp/national_team/staff/MATSUMOTO_Ryoichi.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
       <c r="A9" s="9" t="inlineStr">
         <is>
           <t>GKコーチ</t>
         </is>
       </c>
-      <c r="B9" s="10" t="inlineStr">
+      <c r="B9" s="12" t="inlineStr">
         <is>
           <t>下田 崇</t>
         </is>
       </c>
-      <c r="C9" s="10" t="inlineStr">
+      <c r="C9" s="12" t="inlineStr">
         <is>
           <t>SHIMODA Takashi</t>
+        </is>
+      </c>
+      <c r="D9" s="14" t="inlineStr">
+        <is>
+          <t>https://www.jfa.jp/national_team/staff/SHIMODA_Takashi.html</t>
         </is>
       </c>
     </row>
@@ -2840,145 +3130,145 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:A26"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="15" customHeight="1">
       <c r="A1" s="11" t="inlineStr">
         <is>
           <t>SAMURAI BLUE / FIFAワールドカップ2026 招集メンバー データ</t>
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
           <t>出典: JFA公式サイト, Wikipedia(2026 FIFA World Cup squads), スポーツナビ等</t>
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
           <t>取得日: 2026-06-18</t>
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
           <t>■ データの扱い</t>
         </is>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
           <t>・生年月日/出場/得点 は招集発表時点(2026/5/15)の値。試合ごとに変動するため随時更新してください。</t>
         </is>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
           <t>・年齢はビューア側で生年月日から自動計算されます(列に年齢はありません)。</t>
         </is>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
           <t>・身長/体重/出身地 は各種選手名鑑に基づく参考値です。</t>
         </is>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
           <t>■ 使い方</t>
         </is>
       </c>
     </row>
-    <row r="11">
+    <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
           <t>1. このExcelの『Members』シートを編集 → 保存。</t>
         </is>
       </c>
     </row>
-    <row r="12">
+    <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
           <t>2. ビューア(samurai_blue_2026.html)で『Excelを読み込む』からこのファイルを選択。</t>
         </is>
       </c>
     </row>
-    <row r="13">
+    <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
           <t>3. 列の順番・見出しは変更しないでください(ビューアが見出し名で読み取ります)。</t>
         </is>
       </c>
     </row>
-    <row r="14">
+    <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
           <t>4. 『特徴』『性格』は編集して自由に追記できます。『YouTube』はURLを差し替え可能。</t>
         </is>
       </c>
     </row>
-    <row r="16">
+    <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
           <t>■ 備考</t>
         </is>
       </c>
     </row>
-    <row r="17">
+    <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
           <t>遠藤 航(元キャプテン)は6/12に負傷離脱、町野 修斗が追加招集(現スカッド26名)。</t>
         </is>
       </c>
     </row>
-    <row r="19">
+    <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
           <t>■ Quotes（格言）シート</t>
         </is>
       </c>
     </row>
-    <row r="20">
+    <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
           <t>・区分/人物/格言/カラー(青赤黒白)/出典/出典URL。行追加で格言カードが増えます。取材記事からの抜粋/要約。</t>
         </is>
       </c>
     </row>
-    <row r="22">
+    <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
           <t>■ Marquees（背景の流れるテキスト）</t>
         </is>
       </c>
     </row>
-    <row r="23">
+    <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
           <t>・テキスト/速度(秒,大きいほど遅い)/方向(左右)/スタイル(アウトライン・塗り)/サイズpx/カラー(青赤灰)/縦位置(0-1)。</t>
         </is>
       </c>
     </row>
-    <row r="25">
+    <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
           <t>■ Hashtags（#タグ）</t>
         </is>
       </c>
     </row>
-    <row r="26">
+    <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
           <t>・タグ＋フィルタ列(空欄=装飾, GK/DF/MF・FWで絞り込み)。</t>
@@ -2997,7 +3287,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F31"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
@@ -3039,7 +3329,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="28.5" customHeight="1">
       <c r="A2" s="9" t="inlineStr">
         <is>
           <t>監督</t>
@@ -3050,7 +3340,7 @@
           <t>森保 一</t>
         </is>
       </c>
-      <c r="C2" s="10" t="inlineStr">
+      <c r="C2" s="12" t="inlineStr">
         <is>
           <t>謙虚に、ひたむきに、たくましく</t>
         </is>
@@ -3065,13 +3355,13 @@
           <t>Sportiva</t>
         </is>
       </c>
-      <c r="F2" s="10" t="inlineStr">
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>https://sportiva.shueisha.co.jp/clm/football/jfootball/2025/02/24/post_16/</t>
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="28.5" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
         <is>
           <t>監督</t>
@@ -3082,7 +3372,7 @@
           <t>森保 一</t>
         </is>
       </c>
-      <c r="C3" s="10" t="inlineStr">
+      <c r="C3" s="12" t="inlineStr">
         <is>
           <t>選手の“心”を預かる仕事だと思っています</t>
         </is>
@@ -3097,13 +3387,13 @@
           <t>Sportiva</t>
         </is>
       </c>
-      <c r="F3" s="10" t="inlineStr">
+      <c r="F3" s="12" t="inlineStr">
         <is>
           <t>https://sportiva.shueisha.co.jp/clm/football/jfootball/2025/02/24/post_16/</t>
         </is>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="28.5" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
         <is>
           <t>監督</t>
@@ -3114,7 +3404,7 @@
           <t>森保 一</t>
         </is>
       </c>
-      <c r="C4" s="10" t="inlineStr">
+      <c r="C4" s="12" t="inlineStr">
         <is>
           <t>日本代表の勝利と、日本サッカーの発展のために</t>
         </is>
@@ -3129,13 +3419,13 @@
           <t>Sportiva</t>
         </is>
       </c>
-      <c r="F4" s="10" t="inlineStr">
+      <c r="F4" s="12" t="inlineStr">
         <is>
           <t>https://sportiva.shueisha.co.jp/clm/football/jfootball/2025/02/24/post_16/</t>
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="28.5" customHeight="1">
       <c r="A5" s="9" t="inlineStr">
         <is>
           <t>チーム</t>
@@ -3146,9 +3436,9 @@
           <t>SAMURAI BLUE</t>
         </is>
       </c>
-      <c r="C5" s="10" t="inlineStr">
-        <is>
-          <t>新しい景色を、見に行く。</t>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>最高の景色を2026 FOR OUR GREATEST STAGE</t>
         </is>
       </c>
       <c r="D5" s="9" t="inlineStr">
@@ -3161,13 +3451,13 @@
           <t>JFA</t>
         </is>
       </c>
-      <c r="F5" s="10" t="inlineStr">
+      <c r="F5" s="12" t="inlineStr">
         <is>
           <t>https://www.jfa.jp/samuraiblue/worldcup_2026/canadamexicousa2026/squad/</t>
         </is>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="28.5" customHeight="1">
       <c r="A6" s="9" t="inlineStr">
         <is>
           <t>選手</t>
@@ -3178,7 +3468,7 @@
           <t>鈴木 彩艶</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C6" s="12" t="inlineStr">
         <is>
           <t>これから5大会に出る</t>
         </is>
@@ -3193,13 +3483,13 @@
           <t>日刊ゲンダイ</t>
         </is>
       </c>
-      <c r="F6" s="10" t="inlineStr">
+      <c r="F6" s="12" t="inlineStr">
         <is>
           <t>https://topics.smt.docomo.ne.jp/article/nikkangendai/sports/nikkangendai-1222162</t>
         </is>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="14.25" customHeight="1">
       <c r="A7" s="9" t="inlineStr">
         <is>
           <t>選手</t>
@@ -3210,7 +3500,7 @@
           <t>大迫 敬介</t>
         </is>
       </c>
-      <c r="C7" s="10" t="inlineStr">
+      <c r="C7" s="12" t="inlineStr">
         <is>
           <t>僕は、仕掛けるタイプ</t>
         </is>
@@ -3225,13 +3515,13 @@
           <t>ゲキサカ</t>
         </is>
       </c>
-      <c r="F7" s="10" t="inlineStr">
+      <c r="F7" s="12" t="inlineStr">
         <is>
           <t>https://web.gekisaka.jp/news/detail/?311569-311569-fl=</t>
         </is>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="14.25" customHeight="1">
       <c r="A8" s="9" t="inlineStr">
         <is>
           <t>選手</t>
@@ -3242,7 +3532,7 @@
           <t>早川 友基</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C8" s="12" t="inlineStr">
         <is>
           <t>ミスをしても、すぐに取り返す</t>
         </is>
@@ -3257,13 +3547,13 @@
           <t>サカノワ</t>
         </is>
       </c>
-      <c r="F8" s="10" t="inlineStr">
+      <c r="F8" s="12" t="inlineStr">
         <is>
           <t>https://sakanowa.jp/topics/105981</t>
         </is>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="42.75" customHeight="1">
       <c r="A9" s="9" t="inlineStr">
         <is>
           <t>選手</t>
@@ -3274,7 +3564,7 @@
           <t>菅原 由勢</t>
         </is>
       </c>
-      <c r="C9" s="10" t="inlineStr">
+      <c r="C9" s="12" t="inlineStr">
         <is>
           <t>優勝以外は、考えていない</t>
         </is>
@@ -3289,13 +3579,13 @@
           <t>Goal</t>
         </is>
       </c>
-      <c r="F9" s="10" t="inlineStr">
+      <c r="F9" s="12" t="inlineStr">
         <is>
           <t>https://www.goal.com/jp/%E3%83%AA%E3%82%B9%E3%83%88/2026-0613-sugawara-yukinari-adidas-goal-jp/bltdaaaa8564a7e5b6c</t>
         </is>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="14.25" customHeight="1">
       <c r="A10" s="9" t="inlineStr">
         <is>
           <t>選手</t>
@@ -3306,7 +3596,7 @@
           <t>谷口 彰悟</t>
         </is>
       </c>
-      <c r="C10" s="10" t="inlineStr">
+      <c r="C10" s="12" t="inlineStr">
         <is>
           <t>身体を張って、ゴールを守り切る</t>
         </is>
@@ -3321,13 +3611,13 @@
           <t>JFA</t>
         </is>
       </c>
-      <c r="F10" s="10" t="inlineStr">
+      <c r="F10" s="12" t="inlineStr">
         <is>
           <t>https://www.jfa.jp/samuraiblue/member/taniguchi_shogo.html</t>
         </is>
       </c>
     </row>
-    <row r="11">
+    <row r="11" ht="14.25" customHeight="1">
       <c r="A11" s="9" t="inlineStr">
         <is>
           <t>選手</t>
@@ -3338,7 +3628,7 @@
           <t>板倉 滉</t>
         </is>
       </c>
-      <c r="C11" s="10" t="inlineStr">
+      <c r="C11" s="12" t="inlineStr">
         <is>
           <t>一秒たりとも、気を抜かない</t>
         </is>
@@ -3353,13 +3643,13 @@
           <t>サッカーマガジン</t>
         </is>
       </c>
-      <c r="F11" s="10" t="inlineStr">
+      <c r="F11" s="12" t="inlineStr">
         <is>
           <t>https://soccermagazine.jp/national_A/17755624</t>
         </is>
       </c>
     </row>
-    <row r="12">
+    <row r="12" ht="28.5" customHeight="1">
       <c r="A12" s="9" t="inlineStr">
         <is>
           <t>選手</t>
@@ -3370,7 +3660,7 @@
           <t>渡辺 剛</t>
         </is>
       </c>
-      <c r="C12" s="10" t="inlineStr">
+      <c r="C12" s="12" t="inlineStr">
         <is>
           <t>ワタルくんのぶんも、前へ進む</t>
         </is>
@@ -3385,13 +3675,13 @@
           <t>日刊スポーツ</t>
         </is>
       </c>
-      <c r="F12" s="10" t="inlineStr">
+      <c r="F12" s="12" t="inlineStr">
         <is>
           <t>https://topics.smt.docomo.ne.jp/article/nikkansports/sports/f-sc-tp0-260612-202606120000217</t>
         </is>
       </c>
     </row>
-    <row r="13">
+    <row r="13" ht="28.5" customHeight="1">
       <c r="A13" s="9" t="inlineStr">
         <is>
           <t>選手</t>
@@ -3402,7 +3692,7 @@
           <t>冨安 健洋</t>
         </is>
       </c>
-      <c r="C13" s="10" t="inlineStr">
+      <c r="C13" s="12" t="inlineStr">
         <is>
           <t>僕の仕事は、しっかり守ること</t>
         </is>
@@ -3417,13 +3707,13 @@
           <t>サッカーキング</t>
         </is>
       </c>
-      <c r="F13" s="10" t="inlineStr">
+      <c r="F13" s="12" t="inlineStr">
         <is>
           <t>https://www.soccer-king.jp/news/world/eng/20221119/1710323.html</t>
         </is>
       </c>
     </row>
-    <row r="14">
+    <row r="14" ht="42.75" customHeight="1">
       <c r="A14" s="9" t="inlineStr">
         <is>
           <t>選手</t>
@@ -3434,7 +3724,7 @@
           <t>伊藤 洋輝</t>
         </is>
       </c>
-      <c r="C14" s="10" t="inlineStr">
+      <c r="C14" s="12" t="inlineStr">
         <is>
           <t>圧倒して、勝つ</t>
         </is>
@@ -3449,13 +3739,13 @@
           <t>Goal</t>
         </is>
       </c>
-      <c r="F14" s="10" t="inlineStr">
+      <c r="F14" s="12" t="inlineStr">
         <is>
           <t>https://www.goal.com/jp/%E3%83%8B%E3%83%A5%E3%83%BC%E3%82%B9/20250317-japan-hiroki-ito/bltc8f2ddeb46ae5aee</t>
         </is>
       </c>
     </row>
-    <row r="15">
+    <row r="15" ht="14.25" customHeight="1">
       <c r="A15" s="9" t="inlineStr">
         <is>
           <t>選手</t>
@@ -3466,7 +3756,7 @@
           <t>瀬古 歩夢</t>
         </is>
       </c>
-      <c r="C15" s="10" t="inlineStr">
+      <c r="C15" s="12" t="inlineStr">
         <is>
           <t>骨がパカパカ言っても、走り続ける</t>
         </is>
@@ -3481,13 +3771,13 @@
           <t>footballista</t>
         </is>
       </c>
-      <c r="F15" s="10" t="inlineStr">
+      <c r="F15" s="12" t="inlineStr">
         <is>
           <t>https://www.footballista.jp/special/217681</t>
         </is>
       </c>
     </row>
-    <row r="16">
+    <row r="16" ht="14.25" customHeight="1">
       <c r="A16" s="9" t="inlineStr">
         <is>
           <t>選手</t>
@@ -3498,7 +3788,7 @@
           <t>鈴木 淳之介</t>
         </is>
       </c>
-      <c r="C16" s="10" t="inlineStr">
+      <c r="C16" s="12" t="inlineStr">
         <is>
           <t>出られるなら、どこでもいい</t>
         </is>
@@ -3513,13 +3803,13 @@
           <t>サッカーダイジェスト</t>
         </is>
       </c>
-      <c r="F16" s="10" t="inlineStr">
+      <c r="F16" s="12" t="inlineStr">
         <is>
           <t>https://www.soccerdigestweb.com/news/detail/id=182440</t>
         </is>
       </c>
     </row>
-    <row r="17">
+    <row r="17" ht="28.5" customHeight="1">
       <c r="A17" s="9" t="inlineStr">
         <is>
           <t>選手</t>
@@ -3530,7 +3820,7 @@
           <t>長友 佑都</t>
         </is>
       </c>
-      <c r="C17" s="10" t="inlineStr">
+      <c r="C17" s="12" t="inlineStr">
         <is>
           <t>意志あるところに、道あり</t>
         </is>
@@ -3545,13 +3835,13 @@
           <t>Number</t>
         </is>
       </c>
-      <c r="F17" s="10" t="inlineStr">
+      <c r="F17" s="12" t="inlineStr">
         <is>
           <t>https://number.bunshun.jp/list/meigen/kw/%E9%95%B7%E5%8F%8B%E4%BD%91%E9%83%BD</t>
         </is>
       </c>
     </row>
-    <row r="18">
+    <row r="18" ht="14.25" customHeight="1">
       <c r="A18" s="9" t="inlineStr">
         <is>
           <t>選手</t>
@@ -3562,7 +3852,7 @@
           <t>伊東 純也</t>
         </is>
       </c>
-      <c r="C18" s="10" t="inlineStr">
+      <c r="C18" s="12" t="inlineStr">
         <is>
           <t>苦しい時こそ、頑張る</t>
         </is>
@@ -3577,13 +3867,13 @@
           <t>名言集</t>
         </is>
       </c>
-      <c r="F18" s="10" t="inlineStr">
+      <c r="F18" s="12" t="inlineStr">
         <is>
           <t>https://kando.meigensyu.org/meigen/itojunya.html</t>
         </is>
       </c>
     </row>
-    <row r="19">
+    <row r="19" ht="28.5" customHeight="1">
       <c r="A19" s="9" t="inlineStr">
         <is>
           <t>選手</t>
@@ -3594,7 +3884,7 @@
           <t>鎌田 大地</t>
         </is>
       </c>
-      <c r="C19" s="10" t="inlineStr">
+      <c r="C19" s="12" t="inlineStr">
         <is>
           <t>怖がらず、思い切ってやる</t>
         </is>
@@ -3609,13 +3899,13 @@
           <t>FRIDAY</t>
         </is>
       </c>
-      <c r="F19" s="10" t="inlineStr">
+      <c r="F19" s="12" t="inlineStr">
         <is>
           <t>https://topics.smt.docomo.ne.jp/article/friday/sports/friday-470794</t>
         </is>
       </c>
     </row>
-    <row r="20">
+    <row r="20" ht="28.5" customHeight="1">
       <c r="A20" s="9" t="inlineStr">
         <is>
           <t>選手</t>
@@ -3626,7 +3916,7 @@
           <t>小川 航基</t>
         </is>
       </c>
-      <c r="C20" s="10" t="inlineStr">
+      <c r="C20" s="12" t="inlineStr">
         <is>
           <t>点を取ることに関しては、僕が一番</t>
         </is>
@@ -3641,13 +3931,13 @@
           <t>サッカーキング</t>
         </is>
       </c>
-      <c r="F20" s="10" t="inlineStr">
+      <c r="F20" s="12" t="inlineStr">
         <is>
           <t>https://www.soccer-king.jp/news/japan/national/20260601/2165790.html</t>
         </is>
       </c>
     </row>
-    <row r="21">
+    <row r="21" ht="14.25" customHeight="1">
       <c r="A21" s="9" t="inlineStr">
         <is>
           <t>選手</t>
@@ -3658,7 +3948,7 @@
           <t>前田 大然</t>
         </is>
       </c>
-      <c r="C21" s="10" t="inlineStr">
+      <c r="C21" s="12" t="inlineStr">
         <is>
           <t>走れなくなったら、サッカーを辞める</t>
         </is>
@@ -3673,13 +3963,13 @@
           <t>ABEMA</t>
         </is>
       </c>
-      <c r="F21" s="10" t="inlineStr">
+      <c r="F21" s="12" t="inlineStr">
         <is>
           <t>https://times.abema.tv/fifaworldcup/articles/-/10039804</t>
         </is>
       </c>
     </row>
-    <row r="22">
+    <row r="22" ht="14.25" customHeight="1">
       <c r="A22" s="9" t="inlineStr">
         <is>
           <t>選手</t>
@@ -3690,7 +3980,7 @@
           <t>堂安 律</t>
         </is>
       </c>
-      <c r="C22" s="10" t="inlineStr">
+      <c r="C22" s="12" t="inlineStr">
         <is>
           <t>自分が一番うまいと思って、ピッチに立つ</t>
         </is>
@@ -3705,13 +3995,13 @@
           <t>Anchor</t>
         </is>
       </c>
-      <c r="F22" s="10" t="inlineStr">
+      <c r="F22" s="12" t="inlineStr">
         <is>
           <t>https://anchor.id/column/n11968</t>
         </is>
       </c>
     </row>
-    <row r="23">
+    <row r="23" ht="14.25" customHeight="1">
       <c r="A23" s="9" t="inlineStr">
         <is>
           <t>選手</t>
@@ -3722,7 +4012,7 @@
           <t>上田 綺世</t>
         </is>
       </c>
-      <c r="C23" s="10" t="inlineStr">
+      <c r="C23" s="12" t="inlineStr">
         <is>
           <t>勝負は、一瞬。</t>
         </is>
@@ -3737,13 +4027,13 @@
           <t>REAL SPORTS</t>
         </is>
       </c>
-      <c r="F23" s="10" t="inlineStr">
+      <c r="F23" s="12" t="inlineStr">
         <is>
           <t>https://real-sports.jp/page/articles/725602914885698716/</t>
         </is>
       </c>
     </row>
-    <row r="24">
+    <row r="24" ht="14.25" customHeight="1">
       <c r="A24" s="9" t="inlineStr">
         <is>
           <t>選手</t>
@@ -3754,7 +4044,7 @@
           <t>田中 碧</t>
         </is>
       </c>
-      <c r="C24" s="10" t="inlineStr">
+      <c r="C24" s="12" t="inlineStr">
         <is>
           <t>言葉ではなく、プレーで示す</t>
         </is>
@@ -3769,13 +4059,13 @@
           <t>GOETHE</t>
         </is>
       </c>
-      <c r="F24" s="10" t="inlineStr">
+      <c r="F24" s="12" t="inlineStr">
         <is>
           <t>https://goetheweb.jp/person/article/20230313-ao-tanaka</t>
         </is>
       </c>
     </row>
-    <row r="25">
+    <row r="25" ht="28.5" customHeight="1">
       <c r="A25" s="9" t="inlineStr">
         <is>
           <t>選手</t>
@@ -3786,7 +4076,7 @@
           <t>町野 修斗</t>
         </is>
       </c>
-      <c r="C25" s="10" t="inlineStr">
+      <c r="C25" s="12" t="inlineStr">
         <is>
           <t>這い上がってやる</t>
         </is>
@@ -3801,13 +4091,13 @@
           <t>Sportiva</t>
         </is>
       </c>
-      <c r="F25" s="10" t="inlineStr">
+      <c r="F25" s="12" t="inlineStr">
         <is>
           <t>https://sportiva.shueisha.co.jp/clm/football/jfootball/2023/04/01/j3j1/</t>
         </is>
       </c>
     </row>
-    <row r="26">
+    <row r="26" ht="14.25" customHeight="1">
       <c r="A26" s="9" t="inlineStr">
         <is>
           <t>選手</t>
@@ -3818,7 +4108,7 @@
           <t>中村 敬斗</t>
         </is>
       </c>
-      <c r="C26" s="10" t="inlineStr">
+      <c r="C26" s="12" t="inlineStr">
         <is>
           <t>誰かに言われてやっても、成長しない</t>
         </is>
@@ -3833,13 +4123,13 @@
           <t>サカイク</t>
         </is>
       </c>
-      <c r="F26" s="10" t="inlineStr">
+      <c r="F26" s="12" t="inlineStr">
         <is>
           <t>https://www.sakaiku.jp/column/interview/2025/017218.html</t>
         </is>
       </c>
     </row>
-    <row r="27">
+    <row r="27" ht="28.5" customHeight="1">
       <c r="A27" s="9" t="inlineStr">
         <is>
           <t>選手</t>
@@ -3850,7 +4140,7 @@
           <t>佐野 海舟</t>
         </is>
       </c>
-      <c r="C27" s="10" t="inlineStr">
+      <c r="C27" s="12" t="inlineStr">
         <is>
           <t>奪った後に、もっと早く仕掛ける</t>
         </is>
@@ -3865,13 +4155,13 @@
           <t>サッカーキング</t>
         </is>
       </c>
-      <c r="F27" s="10" t="inlineStr">
+      <c r="F27" s="12" t="inlineStr">
         <is>
           <t>https://www.soccer-king.jp/news/japan/national/20250910/2061603.html</t>
         </is>
       </c>
     </row>
-    <row r="28">
+    <row r="28" ht="14.25" customHeight="1">
       <c r="A28" s="9" t="inlineStr">
         <is>
           <t>選手</t>
@@ -3882,7 +4172,7 @@
           <t>久保 建英</t>
         </is>
       </c>
-      <c r="C28" s="10" t="inlineStr">
+      <c r="C28" s="12" t="inlineStr">
         <is>
           <t>優勝して、トロフィーを持って帰りたい</t>
         </is>
@@ -3897,13 +4187,13 @@
           <t>ゲキサカ</t>
         </is>
       </c>
-      <c r="F28" s="10" t="inlineStr">
+      <c r="F28" s="12" t="inlineStr">
         <is>
           <t>https://web.gekisaka.jp/news/japan/detail/?453213-453213-fl=</t>
         </is>
       </c>
     </row>
-    <row r="29">
+    <row r="29" ht="42.75" customHeight="1">
       <c r="A29" s="9" t="inlineStr">
         <is>
           <t>選手</t>
@@ -3914,7 +4204,7 @@
           <t>鈴木 唯人</t>
         </is>
       </c>
-      <c r="C29" s="10" t="inlineStr">
+      <c r="C29" s="12" t="inlineStr">
         <is>
           <t>律くんのように、成長したい</t>
         </is>
@@ -3929,13 +4219,13 @@
           <t>Goal</t>
         </is>
       </c>
-      <c r="F29" s="10" t="inlineStr">
+      <c r="F29" s="12" t="inlineStr">
         <is>
           <t>https://www.goal.com/jp/%E3%83%8B%E3%83%A5%E3%83%BC%E3%82%B9/bundesliga-freiburg-yuito-suzuki-20250728/blt97f0e28411c91600</t>
         </is>
       </c>
     </row>
-    <row r="30">
+    <row r="30" ht="14.25" customHeight="1">
       <c r="A30" s="9" t="inlineStr">
         <is>
           <t>選手</t>
@@ -3946,7 +4236,7 @@
           <t>塩貝 健人</t>
         </is>
       </c>
-      <c r="C30" s="10" t="inlineStr">
+      <c r="C30" s="12" t="inlineStr">
         <is>
           <t>僕以外、できない</t>
         </is>
@@ -3961,13 +4251,13 @@
           <t>FOOTBALL ZONE</t>
         </is>
       </c>
-      <c r="F30" s="10" t="inlineStr">
+      <c r="F30" s="12" t="inlineStr">
         <is>
           <t>https://www.football-zone.net/archives/633705</t>
         </is>
       </c>
     </row>
-    <row r="31">
+    <row r="31" ht="28.5" customHeight="1">
       <c r="A31" s="9" t="inlineStr">
         <is>
           <t>選手</t>
@@ -3978,7 +4268,7 @@
           <t>後藤 啓介</t>
         </is>
       </c>
-      <c r="C31" s="10" t="inlineStr">
+      <c r="C31" s="12" t="inlineStr">
         <is>
           <t>目をつぶっていても、ゴールを決める</t>
         </is>
@@ -3993,7 +4283,7 @@
           <t>SOCCER DIGEST</t>
         </is>
       </c>
-      <c r="F31" s="10" t="inlineStr">
+      <c r="F31" s="12" t="inlineStr">
         <is>
           <t>https://news.yahoo.co.jp/articles/364e68c42dbb1128709a2957b0e70aade9cc4478</t>
         </is>
@@ -4010,8 +4300,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:G16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
@@ -4059,10 +4349,10 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SAMURAI BLUE ★ FIFA WORLD CUP 2026 ・ CANADA · MEXICO · USA ★ </t>
+    <row r="2" ht="14.25" customHeight="1">
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FIFA WORLD CUP 2026　 CANADA · MEXICO · USA　</t>
         </is>
       </c>
       <c r="B2" s="9" t="n">
@@ -4086,10 +4376,10 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">#新しい景色へ 　#SAMURAIBLUE 　#日本代表 　#WC2026 　#VAMOS 　</t>
+    <row r="3" ht="66.75" customHeight="1">
+      <c r="A3" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#最高の景色を　#SAMURAIBLUE 　#日本代表 　#WC2026 　　</t>
         </is>
       </c>
       <c r="B3" s="9" t="n">
@@ -4117,10 +4407,10 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">謙虚に・ひたむきに・たくましく ／ 勝負は一瞬 ／ 意志あるところに道あり ／ </t>
+    <row r="4" ht="38.25" customHeight="1">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>良い守備から、良い攻撃へ　個の力と組織力　総力戦</t>
         </is>
       </c>
       <c r="B4" s="9" t="n">
@@ -4148,10 +4438,10 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">26 WARRIORS ・ ONE TEAM ・ 世界へ ・ TO THE NEW HORIZON ・ </t>
+    <row r="5" ht="58.5" customHeight="1">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>誇り　責任　礼節　団結　覚悟</t>
         </is>
       </c>
       <c r="B5" s="9" t="n">
@@ -4175,10 +4465,10 @@
         <v>0.58</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">JAPAN NATIONAL TEAM 　日本代表 　ニッポン 　</t>
+    <row r="6" ht="36" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>一戦一戦、最善の準備を尽くす　誰が出ても勝てるチーム　ピッチの上で証明する　すべては勝利のために</t>
         </is>
       </c>
       <c r="B6" s="9" t="n">
@@ -4206,10 +4496,10 @@
         <v>0.76</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">GO FOR THE WORLD ・ 世界を、驚かせ。 ・ #VAMOS_JAPAN ・ </t>
+    <row r="7" ht="68.25" customHeight="1">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JAPAN NATIONAL TEAM   </t>
         </is>
       </c>
       <c r="B7" s="9" t="n">
@@ -4232,6 +4522,10 @@
       <c r="G7" s="9" t="n">
         <v>0.93</v>
       </c>
+    </row>
+    <row r="8" ht="50.25" customHeight="1"/>
+    <row r="16" ht="14.25" customHeight="1">
+      <c r="A16" s="12" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4244,8 +4538,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
@@ -4263,121 +4557,53 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="10" t="inlineStr">
+    <row r="2" ht="14.25" customHeight="1">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>#WC2026</t>
         </is>
       </c>
       <c r="B2" s="9" t="inlineStr"/>
     </row>
-    <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+    <row r="3" ht="14.25" customHeight="1">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>#SAMURAIBLUE</t>
         </is>
       </c>
       <c r="B3" s="9" t="inlineStr"/>
     </row>
-    <row r="4">
-      <c r="A4" s="10" t="inlineStr">
+    <row r="4" ht="14.25" customHeight="1">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>#日本代表</t>
         </is>
       </c>
       <c r="B4" s="9" t="inlineStr"/>
     </row>
-    <row r="5">
-      <c r="A5" s="10" t="inlineStr">
+    <row r="5" ht="14.25" customHeight="1">
+      <c r="A5" s="12" t="inlineStr">
         <is>
           <t>#新しい景色</t>
         </is>
       </c>
       <c r="B5" s="9" t="inlineStr"/>
     </row>
-    <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+    <row r="6" ht="14.25" customHeight="1">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>#VAMOS_JAPAN</t>
         </is>
       </c>
       <c r="B6" s="9" t="inlineStr"/>
     </row>
-    <row r="7">
-      <c r="A7" s="10" t="inlineStr">
+    <row r="7" ht="14.25" customHeight="1">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>#森保JAPAN</t>
         </is>
       </c>
       <c r="B7" s="9" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="10" t="inlineStr">
-        <is>
-          <t>#26人の戦士</t>
-        </is>
-      </c>
-      <c r="B8" s="9" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="10" t="inlineStr">
-        <is>
-          <t>#GroupStage</t>
-        </is>
-      </c>
-      <c r="B9" s="9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="10" t="inlineStr">
-        <is>
-          <t>#青の誇り</t>
-        </is>
-      </c>
-      <c r="B10" s="9" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="10" t="inlineStr">
-        <is>
-          <t>#世界へ</t>
-        </is>
-      </c>
-      <c r="B11" s="9" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="10" t="inlineStr">
-        <is>
-          <t>#GK</t>
-        </is>
-      </c>
-      <c r="B12" s="9" t="inlineStr">
-        <is>
-          <t>GK</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="10" t="inlineStr">
-        <is>
-          <t>#DF</t>
-        </is>
-      </c>
-      <c r="B13" s="9" t="inlineStr">
-        <is>
-          <t>DF</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="10" t="inlineStr">
-        <is>
-          <t>#MF_FW</t>
-        </is>
-      </c>
-      <c r="B14" s="9" t="inlineStr">
-        <is>
-          <t>MF/FW</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/samurai_blue_2026_members.xlsx
+++ b/samurai_blue_2026_members.xlsx
@@ -3470,7 +3470,7 @@
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>これから5大会に出る</t>
+          <t>チャレンジャー精神を、忘れずに</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
@@ -3480,12 +3480,12 @@
       </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
-          <t>日刊ゲンダイ</t>
+          <t>サッカーキング(2026)</t>
         </is>
       </c>
       <c r="F6" s="12" t="inlineStr">
         <is>
-          <t>https://topics.smt.docomo.ne.jp/article/nikkangendai/sports/nikkangendai-1222162</t>
+          <t>https://www.soccer-king.jp/news/japan/national/20260611/2170026.html</t>
         </is>
       </c>
     </row>
@@ -3502,7 +3502,7 @@
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>僕は、仕掛けるタイプ</t>
+          <t>次の大会は、自分が出たい</t>
         </is>
       </c>
       <c r="D7" s="9" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="E7" s="9" t="inlineStr">
         <is>
-          <t>ゲキサカ</t>
+          <t>サンフレッチェ広島(2026)</t>
         </is>
       </c>
       <c r="F7" s="12" t="inlineStr">
         <is>
-          <t>https://web.gekisaka.jp/news/detail/?311569-311569-fl=</t>
+          <t>https://www3.targma.jp/sigmaclub/2026/05/15/post18071/</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>ミスをしても、すぐに取り返す</t>
+          <t>小さい子が“GKをやりたい”と思える選手に</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="E8" s="9" t="inlineStr">
         <is>
-          <t>サカノワ</t>
+          <t>ゲキサカ(2025)</t>
         </is>
       </c>
       <c r="F8" s="12" t="inlineStr">
         <is>
-          <t>https://sakanowa.jp/topics/105981</t>
+          <t>https://web.gekisaka.jp/news/jleague/detail/?442583-442583-fl=</t>
         </is>
       </c>
     </row>
@@ -3576,7 +3576,7 @@
       </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
-          <t>Goal</t>
+          <t>Goal(2026)</t>
         </is>
       </c>
       <c r="F9" s="12" t="inlineStr">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>身体を張って、ゴールを守り切る</t>
+          <t>ピッチ内外で、存在感を出したい</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E10" s="9" t="inlineStr">
         <is>
-          <t>JFA</t>
+          <t>テレ東スポーツ(2025)</t>
         </is>
       </c>
       <c r="F10" s="12" t="inlineStr">
         <is>
-          <t>https://www.jfa.jp/samuraiblue/member/taniguchi_shogo.html</t>
+          <t>https://www.tv-tokyo.co.jp/sports/articles/2025/10/039181.html</t>
         </is>
       </c>
     </row>
@@ -3630,7 +3630,7 @@
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>一秒たりとも、気を抜かない</t>
+          <t>責任と覚悟を持って、引き受けたい</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>サッカーマガジン</t>
+          <t>サッカーキング(2026)</t>
         </is>
       </c>
       <c r="F11" s="12" t="inlineStr">
         <is>
-          <t>https://soccermagazine.jp/national_A/17755624</t>
+          <t>https://www.soccer-king.jp/news/japan/national/20260612/2170362.html</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>ワタルくんのぶんも、前へ進む</t>
+          <t>守備を人の責任にしたくない。自分が統率して守る</t>
         </is>
       </c>
       <c r="D12" s="9" t="inlineStr">
@@ -3672,12 +3672,12 @@
       </c>
       <c r="E12" s="9" t="inlineStr">
         <is>
-          <t>日刊スポーツ</t>
+          <t>サッカーマガジン(2025)</t>
         </is>
       </c>
       <c r="F12" s="12" t="inlineStr">
         <is>
-          <t>https://topics.smt.docomo.ne.jp/article/nikkansports/sports/f-sc-tp0-260612-202606120000217</t>
+          <t>https://soccermagazine.jp/national_A/17795658</t>
         </is>
       </c>
     </row>
@@ -3694,7 +3694,7 @@
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>僕の仕事は、しっかり守ること</t>
+          <t>これからは、自分次第</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr">
@@ -3704,12 +3704,12 @@
       </c>
       <c r="E13" s="9" t="inlineStr">
         <is>
-          <t>サッカーキング</t>
+          <t>サッカーキング(2026)</t>
         </is>
       </c>
       <c r="F13" s="12" t="inlineStr">
         <is>
-          <t>https://www.soccer-king.jp/news/world/eng/20221119/1710323.html</t>
+          <t>https://www.soccer-king.jp/news/japan/national/20260101/2107705.html</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="C14" s="12" t="inlineStr">
         <is>
-          <t>圧倒して、勝つ</t>
+          <t>怪我と批判に負けて、終わるわけがない</t>
         </is>
       </c>
       <c r="D14" s="9" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="E14" s="9" t="inlineStr">
         <is>
-          <t>Goal</t>
+          <t>サッカーキング(2025)</t>
         </is>
       </c>
       <c r="F14" s="12" t="inlineStr">
         <is>
-          <t>https://www.goal.com/jp/%E3%83%8B%E3%83%A5%E3%83%BC%E3%82%B9/20250317-japan-hiroki-ito/bltc8f2ddeb46ae5aee</t>
+          <t>https://www.soccer-king.jp/player/article/444275.html</t>
         </is>
       </c>
     </row>
@@ -3822,7 +3822,7 @@
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>意志あるところに、道あり</t>
+          <t>感謝1000％。すべて称賛に変えて、優勝へ</t>
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr">
@@ -3832,12 +3832,12 @@
       </c>
       <c r="E17" s="9" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>サッカーダイジェスト(2026)</t>
         </is>
       </c>
       <c r="F17" s="12" t="inlineStr">
         <is>
-          <t>https://number.bunshun.jp/list/meigen/kw/%E9%95%B7%E5%8F%8B%E4%BD%91%E9%83%BD</t>
+          <t>https://www.soccerdigestweb.com/news/detail/id=190686</t>
         </is>
       </c>
     </row>
@@ -3854,7 +3854,7 @@
       </c>
       <c r="C18" s="12" t="inlineStr">
         <is>
-          <t>苦しい時こそ、頑張る</t>
+          <t>成長って歳でもないんで、自分の力を出すだけ</t>
         </is>
       </c>
       <c r="D18" s="9" t="inlineStr">
@@ -3864,12 +3864,12 @@
       </c>
       <c r="E18" s="9" t="inlineStr">
         <is>
-          <t>名言集</t>
+          <t>footballista(2026)</t>
         </is>
       </c>
       <c r="F18" s="12" t="inlineStr">
         <is>
-          <t>https://kando.meigensyu.org/meigen/itojunya.html</t>
+          <t>https://www.footballista.jp/special/215299</t>
         </is>
       </c>
     </row>
@@ -3918,7 +3918,7 @@
       </c>
       <c r="C20" s="12" t="inlineStr">
         <is>
-          <t>点を取ることに関しては、僕が一番</t>
+          <t>僕のゴールでも、みんなの勝ち点1</t>
         </is>
       </c>
       <c r="D20" s="9" t="inlineStr">
@@ -3928,12 +3928,12 @@
       </c>
       <c r="E20" s="9" t="inlineStr">
         <is>
-          <t>サッカーキング</t>
+          <t>サッカーマガジン(2026)</t>
         </is>
       </c>
       <c r="F20" s="12" t="inlineStr">
         <is>
-          <t>https://www.soccer-king.jp/news/japan/national/20260601/2165790.html</t>
+          <t>https://soccermagazine.jp/national_A/17845974</t>
         </is>
       </c>
     </row>
@@ -3950,7 +3950,7 @@
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>走れなくなったら、サッカーを辞める</t>
+          <t>とにかく走って、チームのために戦い続ける</t>
         </is>
       </c>
       <c r="D21" s="9" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="E21" s="9" t="inlineStr">
         <is>
-          <t>ABEMA</t>
+          <t>Jリーグ.jp(2026)</t>
         </is>
       </c>
       <c r="F21" s="12" t="inlineStr">
         <is>
-          <t>https://times.abema.tv/fifaworldcup/articles/-/10039804</t>
+          <t>https://www.jleague.jp/special/sb/pride_2026/maeda_daizen.html</t>
         </is>
       </c>
     </row>
@@ -3982,7 +3982,7 @@
       </c>
       <c r="C22" s="12" t="inlineStr">
         <is>
-          <t>自分が一番うまいと思って、ピッチに立つ</t>
+          <t>僕の目標は、優勝すること</t>
         </is>
       </c>
       <c r="D22" s="9" t="inlineStr">
@@ -3992,12 +3992,12 @@
       </c>
       <c r="E22" s="9" t="inlineStr">
         <is>
-          <t>Anchor</t>
+          <t>サッカーキング(2026)</t>
         </is>
       </c>
       <c r="F22" s="12" t="inlineStr">
         <is>
-          <t>https://anchor.id/column/n11968</t>
+          <t>https://www.soccer-king.jp/news/japan/national/20260614/2171499.html</t>
         </is>
       </c>
     </row>
@@ -4014,7 +4014,7 @@
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>勝負は、一瞬。</t>
+          <t>僕の一番の原動力は、家族です</t>
         </is>
       </c>
       <c r="D23" s="9" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="E23" s="9" t="inlineStr">
         <is>
-          <t>REAL SPORTS</t>
+          <t>サッカーキング(2026)</t>
         </is>
       </c>
       <c r="F23" s="12" t="inlineStr">
         <is>
-          <t>https://real-sports.jp/page/articles/725602914885698716/</t>
+          <t>https://www.soccer-king.jp/news/japan/national/20260621/2175194.html</t>
         </is>
       </c>
     </row>
@@ -4046,7 +4046,7 @@
       </c>
       <c r="C24" s="12" t="inlineStr">
         <is>
-          <t>言葉ではなく、プレーで示す</t>
+          <t>個人的には、1人じゃない</t>
         </is>
       </c>
       <c r="D24" s="9" t="inlineStr">
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E24" s="9" t="inlineStr">
         <is>
-          <t>GOETHE</t>
+          <t>サッカーキング(2026)</t>
         </is>
       </c>
       <c r="F24" s="12" t="inlineStr">
         <is>
-          <t>https://goetheweb.jp/person/article/20230313-ao-tanaka</t>
+          <t>https://www.soccer-king.jp/news/japan/national/20260621/2175149.html</t>
         </is>
       </c>
     </row>
@@ -4078,7 +4078,7 @@
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>這い上がってやる</t>
+          <t>“町野で良かった”と思える大会にしたい</t>
         </is>
       </c>
       <c r="D25" s="9" t="inlineStr">
@@ -4088,12 +4088,12 @@
       </c>
       <c r="E25" s="9" t="inlineStr">
         <is>
-          <t>Sportiva</t>
+          <t>スポニチ(2026)</t>
         </is>
       </c>
       <c r="F25" s="12" t="inlineStr">
         <is>
-          <t>https://sportiva.shueisha.co.jp/clm/football/jfootball/2023/04/01/j3j1/</t>
+          <t>https://news.yahoo.co.jp/articles/9109ec52dc022520c5f17603b874cd7a995d06b7</t>
         </is>
       </c>
     </row>
@@ -4110,7 +4110,7 @@
       </c>
       <c r="C26" s="12" t="inlineStr">
         <is>
-          <t>誰かに言われてやっても、成長しない</t>
+          <t>狙い通りの、ゴール</t>
         </is>
       </c>
       <c r="D26" s="9" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="E26" s="9" t="inlineStr">
         <is>
-          <t>サカイク</t>
+          <t>サッカーキング(2026)</t>
         </is>
       </c>
       <c r="F26" s="12" t="inlineStr">
         <is>
-          <t>https://www.sakaiku.jp/column/interview/2025/017218.html</t>
+          <t>https://www.soccer-king.jp/news/japan/national/20260615/2171947.html</t>
         </is>
       </c>
     </row>
@@ -4142,7 +4142,7 @@
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>奪った後に、もっと早く仕掛ける</t>
+          <t>勝ちたいという姿勢を見せないと、何も変わらない</t>
         </is>
       </c>
       <c r="D27" s="9" t="inlineStr">
@@ -4152,12 +4152,12 @@
       </c>
       <c r="E27" s="9" t="inlineStr">
         <is>
-          <t>サッカーキング</t>
+          <t>スポーツナビ(2025)</t>
         </is>
       </c>
       <c r="F27" s="12" t="inlineStr">
         <is>
-          <t>https://www.soccer-king.jp/news/japan/national/20250910/2061603.html</t>
+          <t>https://sports.yahoo.co.jp/column/detail/2025121000001-spnavi</t>
         </is>
       </c>
     </row>
@@ -4174,7 +4174,7 @@
       </c>
       <c r="C28" s="12" t="inlineStr">
         <is>
-          <t>優勝して、トロフィーを持って帰りたい</t>
+          <t>僕たちは、勝ちます</t>
         </is>
       </c>
       <c r="D28" s="9" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="E28" s="9" t="inlineStr">
         <is>
-          <t>ゲキサカ</t>
+          <t>日刊スポーツ(2026)</t>
         </is>
       </c>
       <c r="F28" s="12" t="inlineStr">
         <is>
-          <t>https://web.gekisaka.jp/news/japan/detail/?453213-453213-fl=</t>
+          <t>https://news.yahoo.co.jp/articles/d750c7dc822188ae4cb140d9f3b962cc5f33f521</t>
         </is>
       </c>
     </row>
@@ -4206,7 +4206,7 @@
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>律くんのように、成長したい</t>
+          <t>まだまだ、プレーで示さないといけない</t>
         </is>
       </c>
       <c r="D29" s="9" t="inlineStr">
@@ -4216,12 +4216,12 @@
       </c>
       <c r="E29" s="9" t="inlineStr">
         <is>
-          <t>Goal</t>
+          <t>サッカーキング(2025)</t>
         </is>
       </c>
       <c r="F29" s="12" t="inlineStr">
         <is>
-          <t>https://www.goal.com/jp/%E3%83%8B%E3%83%A5%E3%83%BC%E3%82%B9/bundesliga-freiburg-yuito-suzuki-20250728/blt97f0e28411c91600</t>
+          <t>https://www.soccer-king.jp/news/japan/national/20250605/2025641.html</t>
         </is>
       </c>
     </row>
@@ -4238,7 +4238,7 @@
       </c>
       <c r="C30" s="12" t="inlineStr">
         <is>
-          <t>僕以外、できない</t>
+          <t>目標は、W杯得点王</t>
         </is>
       </c>
       <c r="D30" s="9" t="inlineStr">
@@ -4248,12 +4248,12 @@
       </c>
       <c r="E30" s="9" t="inlineStr">
         <is>
-          <t>FOOTBALL ZONE</t>
+          <t>サッカーキング(2026)</t>
         </is>
       </c>
       <c r="F30" s="12" t="inlineStr">
         <is>
-          <t>https://www.football-zone.net/archives/633705</t>
+          <t>https://news.yahoo.co.jp/articles/348b124799e607d9a3ab1fb22fb44153bde996fa</t>
         </is>
       </c>
     </row>
@@ -4270,7 +4270,7 @@
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>目をつぶっていても、ゴールを決める</t>
+          <t>移籍を、正解にできた</t>
         </is>
       </c>
       <c r="D31" s="9" t="inlineStr">
@@ -4280,12 +4280,12 @@
       </c>
       <c r="E31" s="9" t="inlineStr">
         <is>
-          <t>SOCCER DIGEST</t>
+          <t>超WORLDサッカー(2026)</t>
         </is>
       </c>
       <c r="F31" s="12" t="inlineStr">
         <is>
-          <t>https://news.yahoo.co.jp/articles/364e68c42dbb1128709a2957b0e70aade9cc4478</t>
+          <t>https://web.ultra-soccer.jp/news/all/23733/</t>
         </is>
       </c>
     </row>
